--- a/exports/colleges/26007_iit-kharagpur-indian-institute-of-technology-iitkgp-kharagpur.xlsx
+++ b/exports/colleges/26007_iit-kharagpur-indian-institute-of-technology-iitkgp-kharagpur.xlsx
@@ -445,7 +445,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="175" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #24</t>
+          <t>Rank #5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.13 Lakhs</t>
+          <t>2.13 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GATE, COAP</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 May - 10 Jul 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.81 Lakhs</t>
+          <t>11.81 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Science</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5 Lakhs</t>
+          <t>1.5 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Postgraduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Feb - 31 Mar 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 55% + IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IIT JAM, JOAPS</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bachelor of Science [BS]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.81 Lakhs</t>
+          <t>11.81 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 June - 12 Jun 2025</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Master of Science [M.Sc] + Ph.D</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Master of Science [M.Sc] + Ph.D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.81 Lakhs</t>
+          <t>32,981</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1064,25 +1064,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M.Sc (General)</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10,000 - 82,600</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>14.73 L</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1095,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1122,12 +1126,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BS (General)</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1137,10 +1141,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.81 Lakhs - 14.73 Lakhs</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>14.73 L</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1158,7 +1166,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 June - 18 Jun 2024</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1180,25 +1188,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B.Arch (General)</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.73 Lakhs</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>13.04 L</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1211,12 +1223,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>24 Dec - 05 Feb 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1226,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1250,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L.L.M</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L.L.M (General)</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1253,10 +1265,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.95 Lakhs</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>5.95 L</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1269,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Dec - 27 Feb 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1296,12 +1312,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Bachelor of Laws [L.L.B.] {Hons.} (Intellectual Property Law)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Bachelor of Laws [L.L.B.] {Hons.} (Intellectual Property Law)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1311,12 +1327,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5 Lakhs - 27.1 Lakhs</t>
+          <t>7.63 L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1331,12 +1347,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Dec - 27 Feb 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1346,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1358,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master in Medical Science &amp; Technology [MMST]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Master in Medical Science &amp; Technology [MMST]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5 Lakhs - 27.1 Lakhs</t>
+          <t>2.13 L</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1388,12 +1404,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1408,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1420,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Human Resource Management [MHRM]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Master of Human Resource Management [MHRM]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5 Lakhs - 27.1 Lakhs</t>
+          <t>5 L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1450,17 +1466,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>24 Dec - 05 Feb 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1470,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1498,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Certification (General)</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1497,10 +1513,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>2.13 L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1518,7 +1538,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 May - 10 Jul 2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1545,22 +1565,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Post Graduate Diploma in Management [PGDM] (Business Analytics)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Post Graduate Diploma in Management [PGDM] (Business Analytics)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.04 Lakhs</t>
+          <t>27.1 L</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1580,7 +1600,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>24 Dec - 05 Feb 2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1602,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Post Doctoral Programme in Law</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Post Doctoral Programme in Law</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.04 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1632,17 +1652,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Feb - 31 Mar 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1652,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1664,55 +1684,1523 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Certificate in Excellence in Research</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Certificate in Excellence in Research</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Management Development Programme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Management Development Programme</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Post Doctoral Fellowship Programme</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Post Doctoral Fellowship Programme</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5 Feb - 31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [B.Sc] + Bachelor of Education [B.Ed]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [B.Sc] + Bachelor of Education [B.Ed]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2.7 L</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M.Tech</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Master of Technology [M.Tech] + Ph.D</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Master of Technology [M.Tech] + Ph.D</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>92150</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>GATE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17 May - 10 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>MBA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Executive Master of Business Administration [EMBA]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Executive Master of Business Administration [EMBA]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8 L</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>27 Aug - 22 Sept 2026</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [BS] + Master of Science [MS]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>14.73 L</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NEET PG</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3 June - 12 Jun 2025</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Master of Arts [M.A.] (Public Policy, Law and Governance)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Master of Arts [M.A.] (Public Policy, Law and Governance)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>9.95 L</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M.Tech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Master of Technology [M.Tech]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Master of Technology [M.Tech]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2.13 Lakhs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Graduation + GATE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>GATE, COAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bachelor of Technology [B.Tech]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bachelor of Technology [B.Tech]</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>11.81 Lakhs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>10+2 with 75% + JEE Advanced</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JEE Advanced</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>M.Phil/Ph.D in Science</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Postgraduation</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Master of Science [M.Sc]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Master of Science [M.Sc]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>82,600</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Graduation with 55% + IIT JAM</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>IIT JAM, JOAPS</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [BS]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bachelor of Science [BS]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11.81 Lakhs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10+2 with 75% + JEE Advanced</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>11.81 Lakhs</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>JEE Advanced</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>M.Sc (General)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10,000 - 82,600</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BS (General)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>11.81 Lakhs - 14.73 Lakhs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B.Arch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B.Arch (General)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>14.73 Lakhs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>L.L.M</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>L.L.M (General)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5.95 Lakhs</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>5 Lakhs - 27.1 Lakhs</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5 Lakhs - 27.1 Lakhs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Telecommunication Systems Management</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Telecommunication Systems Management</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>5 Lakhs - 27.1 Lakhs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Certification (General)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>13.04 Lakhs</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>2 Years</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>13.04 Lakhs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Graduation with 60%+</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>CAT</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>26007</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13.04 Lakhs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -1866,12 +3354,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2,44,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24,30,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1901,13 +3389,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1918,17 +3404,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -1940,15 +3416,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #24</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
